--- a/data/trans_dic/P3A_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,56</t>
+          <t>1,51; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,2</t>
+          <t>1,3; 4,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,23</t>
+          <t>0,73; 3,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,75</t>
+          <t>0,67; 7,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,85</t>
+          <t>0,59; 2,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,58</t>
+          <t>0,66; 3,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,26</t>
+          <t>0,25; 2,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,09</t>
+          <t>0,49; 4,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,19</t>
+          <t>1,38; 3,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,2</t>
+          <t>1,28; 3,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,3</t>
+          <t>0,72; 2,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,09</t>
+          <t>1,06; 4,86</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,59</t>
+          <t>2,11; 4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,4</t>
+          <t>0,98; 3,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,0</t>
+          <t>0,94; 3,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,91</t>
+          <t>0,82; 2,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,54</t>
+          <t>0,53; 2,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,07</t>
+          <t>0,18; 2,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,56</t>
+          <t>1,71; 3,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,68</t>
+          <t>1,16; 2,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,99</t>
+          <t>0,18; 2,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,46</t>
+          <t>3,82; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,95</t>
+          <t>1,41; 4,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,95</t>
+          <t>0,42; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,45</t>
+          <t>0,93; 3,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,74</t>
+          <t>1,47; 3,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,05</t>
+          <t>1,47; 3,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,32</t>
+          <t>0,4; 2,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,0</t>
+          <t>0,53; 2,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,86</t>
+          <t>2,84; 5,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,54</t>
+          <t>1,61; 3,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,78</t>
+          <t>0,56; 1,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,17</t>
+          <t>0,84; 2,28</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,95</t>
+          <t>2,33; 5,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,44</t>
+          <t>1,56; 4,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,28</t>
+          <t>0,45; 2,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,57</t>
+          <t>0,81; 3,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,61</t>
+          <t>0,91; 3,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,54</t>
+          <t>1,51; 4,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,37</t>
+          <t>0,62; 2,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,08</t>
+          <t>1,88; 3,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,14</t>
+          <t>1,91; 4,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,93</t>
+          <t>1,82; 3,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,94</t>
+          <t>0,65; 2,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,28</t>
+          <t>1,39; 3,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,96</t>
+          <t>1,94; 6,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,79</t>
+          <t>1,67; 5,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,62</t>
+          <t>2,2; 6,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,05</t>
+          <t>2,16; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,8</t>
+          <t>0,99; 3,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,78</t>
+          <t>2,47; 6,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,93</t>
+          <t>0,45; 2,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,93</t>
+          <t>1,7; 4,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,11</t>
+          <t>1,79; 4,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,2</t>
+          <t>2,46; 5,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,98</t>
+          <t>1,63; 4,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,07</t>
+          <t>2,23; 4,02</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,4</t>
+          <t>1,43; 5,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,43</t>
+          <t>3,67; 9,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,64</t>
+          <t>0,59; 3,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,93</t>
+          <t>4,86; 8,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,43</t>
+          <t>3,5; 8,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,47</t>
+          <t>2,93; 7,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,24</t>
+          <t>2,31; 6,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,89</t>
+          <t>1,56; 7,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,1</t>
+          <t>2,96; 6,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,31</t>
+          <t>3,77; 7,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,27</t>
+          <t>1,63; 4,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,52</t>
+          <t>2,72; 7,57</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 13,36</t>
+          <t>5,98; 13,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,56; 22,31</t>
+          <t>12,24; 22,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 18,55</t>
+          <t>10,28; 18,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,54; 26,32</t>
+          <t>18,47; 26,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 14,57</t>
+          <t>7,28; 14,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,31; 23,72</t>
+          <t>15,16; 23,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,12; 19,53</t>
+          <t>10,92; 19,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,09; 31,3</t>
+          <t>25,1; 31,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 13,23</t>
+          <t>7,69; 12,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,46; 21,86</t>
+          <t>15,51; 21,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,43; 17,41</t>
+          <t>11,81; 17,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,23; 27,94</t>
+          <t>23,28; 28,11</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,77</t>
+          <t>3,4; 4,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,51</t>
+          <t>3,13; 4,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,01</t>
+          <t>1,9; 2,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,19</t>
+          <t>3,34; 5,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,81</t>
+          <t>2,55; 3,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,42</t>
+          <t>3,81; 5,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,73</t>
+          <t>2,48; 3,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,02</t>
+          <t>4,23; 6,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,08</t>
+          <t>3,15; 4,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,69</t>
+          <t>3,75; 4,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,18</t>
+          <t>2,3; 3,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,45</t>
+          <t>4,18; 5,44</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7936; 22507</t>
+          <t>7458; 21690</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5064; 19069</t>
+          <t>5888; 19090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2952; 13475</t>
+          <t>3067; 14420</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2702; 27008</t>
+          <t>2670; 29090</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3528; 13322</t>
+          <t>2760; 13422</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2895; 15382</t>
+          <t>2847; 15791</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1024; 8934</t>
+          <t>1001; 9761</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1530; 12814</t>
+          <t>1546; 14320</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14306; 30668</t>
+          <t>13232; 30943</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10956; 28282</t>
+          <t>11334; 28503</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5730; 18706</t>
+          <t>5878; 18289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8053; 36267</t>
+          <t>7553; 34659</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14641; 33744</t>
+          <t>15488; 35056</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6740; 23366</t>
+          <t>6748; 21415</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9500</t>
+          <t>0; 7993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 16328</t>
+          <t>0; 16230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5220; 18714</t>
+          <t>5860; 19399</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4976; 17788</t>
+          <t>5002; 17889</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2934; 14304</t>
+          <t>3004; 15209</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>976; 10597</t>
+          <t>947; 10336</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25113; 48328</t>
+          <t>23194; 47113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14449; 34796</t>
+          <t>15091; 34743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4946; 18369</t>
+          <t>4969; 18362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2027; 18610</t>
+          <t>1642; 19630</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23207; 47553</t>
+          <t>24386; 47838</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8624; 26943</t>
+          <t>9611; 28174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2794; 13028</t>
+          <t>2804; 12957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4773; 18495</t>
+          <t>4963; 18642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9909; 25788</t>
+          <t>10146; 25299</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10293; 28744</t>
+          <t>10469; 27744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2648; 15295</t>
+          <t>2615; 14862</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2988; 11814</t>
+          <t>3145; 12088</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36357; 64522</t>
+          <t>37675; 66464</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22338; 49229</t>
+          <t>22440; 46574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7741; 23592</t>
+          <t>7483; 22777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9324; 24449</t>
+          <t>9453; 25764</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12297; 30876</t>
+          <t>12115; 30752</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9512; 27318</t>
+          <t>9583; 28170</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2937; 14640</t>
+          <t>2889; 14517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7182; 31680</t>
+          <t>7157; 30961</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5029; 18621</t>
+          <t>4704; 18555</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9096; 27999</t>
+          <t>9289; 27619</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3935; 15362</t>
+          <t>4041; 15219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13588; 29086</t>
+          <t>13409; 28118</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20177; 42807</t>
+          <t>19775; 43687</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22733; 48430</t>
+          <t>22441; 46964</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8262; 25096</t>
+          <t>8367; 25985</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22629; 52546</t>
+          <t>22290; 53493</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7395; 23060</t>
+          <t>7509; 24062</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6254; 20505</t>
+          <t>7153; 21500</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10268; 31638</t>
+          <t>10513; 30029</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12115; 28360</t>
+          <t>12118; 28726</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3914; 15327</t>
+          <t>4009; 15604</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11301; 30382</t>
+          <t>11055; 28531</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3349; 14543</t>
+          <t>2232; 12751</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9622; 21507</t>
+          <t>9318; 22066</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13227; 32449</t>
+          <t>14123; 33294</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21761; 45604</t>
+          <t>21546; 44835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16613; 38752</t>
+          <t>15891; 38945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24343; 45170</t>
+          <t>24742; 44639</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4232; 15791</t>
+          <t>4172; 15640</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11348; 29199</t>
+          <t>11378; 30333</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2068; 12132</t>
+          <t>1974; 11408</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17310; 32780</t>
+          <t>17849; 32366</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12399; 28893</t>
+          <t>11997; 27706</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9756; 26369</t>
+          <t>10328; 26747</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8498; 23523</t>
+          <t>8707; 24513</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10772; 47967</t>
+          <t>9456; 48159</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17643; 38793</t>
+          <t>18780; 39357</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24365; 48464</t>
+          <t>24995; 47651</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11560; 30298</t>
+          <t>11609; 30373</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27433; 73357</t>
+          <t>26471; 73807</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12364; 28047</t>
+          <t>12555; 27648</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31390; 55752</t>
+          <t>30587; 55830</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26632; 47524</t>
+          <t>26338; 47271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52437; 74415</t>
+          <t>52214; 74921</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24873; 48664</t>
+          <t>24313; 48517</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59552; 92266</t>
+          <t>58983; 92136</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44499; 78157</t>
+          <t>43707; 78197</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>106849; 133273</t>
+          <t>106890; 132502</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41804; 71926</t>
+          <t>41811; 70223</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>98744; 139676</t>
+          <t>99083; 139168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>75027; 114279</t>
+          <t>77516; 116073</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>164623; 197970</t>
+          <t>164940; 199188</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>110225; 156128</t>
+          <t>111528; 161196</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107733; 154617</t>
+          <t>107120; 156295</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66300; 101792</t>
+          <t>64369; 100996</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>115754; 179417</t>
+          <t>115599; 174998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>87566; 128710</t>
+          <t>86206; 126266</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>139713; 192863</t>
+          <t>135629; 188487</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>84935; 132123</t>
+          <t>87941; 132776</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>165465; 223279</t>
+          <t>157053; 225152</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>211408; 271328</t>
+          <t>209386; 269777</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>260008; 327290</t>
+          <t>261714; 328811</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>162745; 220265</t>
+          <t>158996; 218791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>303718; 390597</t>
+          <t>299741; 389766</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,39</t>
+          <t>1,65; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,2</t>
+          <t>1,3; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,45</t>
+          <t>0,74; 3,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,27</t>
+          <t>0,7; 7,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,88</t>
+          <t>0,75; 2,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,67</t>
+          <t>0,65; 3,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,47</t>
+          <t>0,25; 2,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,57</t>
+          <t>0,39; 3,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,22</t>
+          <t>1,39; 3,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,22</t>
+          <t>1,23; 3,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,25</t>
+          <t>0,74; 2,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,86</t>
+          <t>1,06; 4,49</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,77</t>
+          <t>2,14; 4,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,12</t>
+          <t>0,97; 3,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,11</t>
+          <t>0,96; 3,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,93</t>
+          <t>0,89; 3,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,7</t>
+          <t>0,5; 2,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,02</t>
+          <t>0,21; 2,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,47</t>
+          <t>1,8; 3,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,68</t>
+          <t>1,14; 2,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,59</t>
+          <t>0,42; 1,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,1</t>
+          <t>0,22; 2,88</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,5</t>
+          <t>3,71; 7,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,13</t>
+          <t>1,26; 4,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,94</t>
+          <t>0,42; 1,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,48</t>
+          <t>0,93; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,67</t>
+          <t>1,46; 3,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,91</t>
+          <t>1,43; 4,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,25</t>
+          <t>0,39; 2,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,04</t>
+          <t>0,6; 2,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,01</t>
+          <t>2,84; 4,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,35</t>
+          <t>1,65; 3,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,72</t>
+          <t>0,53; 1,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,28</t>
+          <t>0,92; 2,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,92</t>
+          <t>2,32; 6,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,58</t>
+          <t>1,52; 4,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,26</t>
+          <t>0,46; 2,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,49</t>
+          <t>1,8; 4,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,6</t>
+          <t>0,98; 3,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,48</t>
+          <t>1,53; 4,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,35</t>
+          <t>0,6; 2,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,95</t>
+          <t>1,97; 3,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,22</t>
+          <t>1,96; 4,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,82</t>
+          <t>1,87; 3,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,01</t>
+          <t>0,7; 1,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,34</t>
+          <t>2,16; 3,8</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,22</t>
+          <t>1,92; 6,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,02</t>
+          <t>1,51; 5,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,28</t>
+          <t>2,19; 6,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,12</t>
+          <t>2,16; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,87</t>
+          <t>0,92; 3,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,37</t>
+          <t>2,48; 6,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,57</t>
+          <t>0,67; 2,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,03</t>
+          <t>1,69; 3,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,22</t>
+          <t>1,68; 4,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,12</t>
+          <t>2,51; 5,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,0</t>
+          <t>1,68; 3,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,02</t>
+          <t>2,14; 3,97</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,35</t>
+          <t>1,43; 5,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,79</t>
+          <t>3,7; 9,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,42</t>
+          <t>0,59; 3,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,82</t>
+          <t>4,66; 8,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,08</t>
+          <t>3,32; 7,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,58</t>
+          <t>2,56; 7,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,51</t>
+          <t>2,25; 6,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,92</t>
+          <t>5,89; 9,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,19</t>
+          <t>3,11; 6,36</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,19</t>
+          <t>3,64; 7,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,28</t>
+          <t>1,8; 4,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,57</t>
+          <t>5,86; 8,74</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,17</t>
+          <t>5,92; 13,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,24; 22,35</t>
+          <t>13,03; 22,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,28; 18,45</t>
+          <t>10,07; 18,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,47; 26,5</t>
+          <t>18,11; 25,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 14,53</t>
+          <t>7,34; 14,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,16; 23,69</t>
+          <t>15,52; 24,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,92; 19,54</t>
+          <t>10,84; 19,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,1; 31,12</t>
+          <t>25,16; 31,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,91</t>
+          <t>7,49; 12,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 21,78</t>
+          <t>15,45; 21,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,81; 17,68</t>
+          <t>11,53; 17,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,28; 28,11</t>
+          <t>23,17; 28,12</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,92</t>
+          <t>3,41; 4,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,56</t>
+          <t>3,11; 4,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,98</t>
+          <t>1,96; 2,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,06</t>
+          <t>3,94; 5,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,74</t>
+          <t>2,57; 3,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,3</t>
+          <t>3,81; 5,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,75</t>
+          <t>2,48; 3,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,07</t>
+          <t>5,22; 6,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,06</t>
+          <t>3,18; 4,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 4,71</t>
+          <t>3,68; 4,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,16</t>
+          <t>2,35; 3,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,44</t>
+          <t>4,77; 5,73</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17263</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7458; 21690</t>
+          <t>8135; 22518</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5888; 19090</t>
+          <t>5912; 18152</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3067; 14420</t>
+          <t>3086; 13776</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2670; 29090</t>
+          <t>2847; 29230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2760; 13422</t>
+          <t>3514; 13456</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2847; 15791</t>
+          <t>2808; 15518</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1001; 9761</t>
+          <t>997; 9123</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1546; 14320</t>
+          <t>1421; 14131</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13232; 30943</t>
+          <t>13339; 31373</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11334; 28503</t>
+          <t>10906; 28420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5878; 18289</t>
+          <t>6005; 18584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7553; 34659</t>
+          <t>8139; 34625</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7870</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15488; 35056</t>
+          <t>15770; 34424</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6748; 21415</t>
+          <t>6647; 22133</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7993</t>
+          <t>0; 8417</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 16230</t>
+          <t>0; 22625</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5860; 19399</t>
+          <t>5956; 19550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5002; 17889</t>
+          <t>5410; 19689</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3004; 15209</t>
+          <t>2803; 14480</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>947; 10336</t>
+          <t>1076; 11204</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23194; 47113</t>
+          <t>24424; 48396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15091; 34743</t>
+          <t>14774; 33610</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4969; 18362</t>
+          <t>4866; 18885</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1642; 19630</t>
+          <t>2166; 28174</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>18278</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24386; 47838</t>
+          <t>23656; 47990</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9611; 28174</t>
+          <t>8592; 27611</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2804; 12957</t>
+          <t>2772; 12823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4963; 18642</t>
+          <t>5750; 20043</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10146; 25299</t>
+          <t>10079; 26071</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10469; 27744</t>
+          <t>10165; 28523</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2615; 14862</t>
+          <t>2607; 14828</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3145; 12088</t>
+          <t>3737; 13323</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37675; 66464</t>
+          <t>37712; 66192</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22440; 46574</t>
+          <t>22973; 48345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7483; 22777</t>
+          <t>7004; 22067</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9453; 25764</t>
+          <t>11413; 28197</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18562</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>41858</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12115; 30752</t>
+          <t>12059; 31773</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9583; 28170</t>
+          <t>9343; 27428</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2889; 14517</t>
+          <t>2950; 15550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7157; 30961</t>
+          <t>12619; 31010</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4704; 18555</t>
+          <t>5030; 18177</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9289; 27619</t>
+          <t>9434; 28907</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4041; 15219</t>
+          <t>3868; 15277</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13409; 28118</t>
+          <t>14519; 28010</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19775; 43687</t>
+          <t>20263; 42338</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22441; 46964</t>
+          <t>22962; 48481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8367; 25985</t>
+          <t>8983; 25172</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22290; 53493</t>
+          <t>30974; 54565</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>35686</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7509; 24062</t>
+          <t>7434; 23959</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7153; 21500</t>
+          <t>6474; 21415</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10513; 30029</t>
+          <t>10444; 30772</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12118; 28726</t>
+          <t>13166; 30555</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4009; 15604</t>
+          <t>3715; 15467</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11055; 28531</t>
+          <t>11110; 29318</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2232; 12751</t>
+          <t>3310; 14791</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9318; 22066</t>
+          <t>10307; 21988</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14123; 33294</t>
+          <t>13239; 31908</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21546; 44835</t>
+          <t>22007; 44786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15891; 38945</t>
+          <t>16370; 38122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24742; 44639</t>
+          <t>26081; 48356</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>60861</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4172; 15640</t>
+          <t>4197; 16622</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11378; 30333</t>
+          <t>11464; 29673</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1974; 11408</t>
+          <t>1960; 11088</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17849; 32366</t>
+          <t>18919; 35568</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11997; 27706</t>
+          <t>11397; 27228</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10328; 26747</t>
+          <t>9021; 25995</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8707; 24513</t>
+          <t>8467; 23544</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9456; 48159</t>
+          <t>25842; 42400</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18780; 39357</t>
+          <t>19789; 40445</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24995; 47651</t>
+          <t>24141; 48050</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11609; 30373</t>
+          <t>12768; 31420</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26471; 73807</t>
+          <t>49469; 73795</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62418</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>119018</t>
+          <t>130695</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>181436</t>
+          <t>197962</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12555; 27648</t>
+          <t>12428; 28521</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30587; 55830</t>
+          <t>32550; 56429</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26338; 47271</t>
+          <t>25808; 46865</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52214; 74921</t>
+          <t>56186; 79375</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24313; 48517</t>
+          <t>24513; 46937</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58983; 92136</t>
+          <t>60383; 93863</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43707; 78197</t>
+          <t>43378; 76499</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>106890; 132502</t>
+          <t>116876; 145839</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41811; 70223</t>
+          <t>40705; 68481</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99083; 139168</t>
+          <t>98679; 138443</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77516; 116073</t>
+          <t>75697; 115180</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>164940; 199188</t>
+          <t>179485; 217854</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149050</t>
+          <t>161420</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>198729</t>
+          <t>218358</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>347779</t>
+          <t>379778</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>111528; 161196</t>
+          <t>111755; 157176</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107120; 156295</t>
+          <t>106620; 154326</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>64369; 100996</t>
+          <t>66300; 100802</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>115599; 174998</t>
+          <t>139060; 189508</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>86206; 126266</t>
+          <t>86834; 128260</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>135629; 188487</t>
+          <t>135337; 187871</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>87941; 132776</t>
+          <t>87896; 132928</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>157053; 225152</t>
+          <t>195052; 241052</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>209386; 269777</t>
+          <t>211271; 270028</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>261714; 328811</t>
+          <t>256649; 329203</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>158996; 218791</t>
+          <t>162606; 221779</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>299741; 389766</t>
+          <t>346329; 416088</t>
         </is>
       </c>
     </row>
